--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N118_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N118_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>33.1085269788322</v>
+        <v>5.380135634060232</v>
       </c>
       <c r="D2" t="n">
-        <v>8.334800040994148</v>
+        <v>1.354405006661549</v>
       </c>
       <c r="E2" t="n">
-        <v>35.80354550179531</v>
+        <v>5.818076144041738</v>
       </c>
       <c r="F2" t="n">
-        <v>20.41757420637694</v>
+        <v>3.317855808536253</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>16.48968465150291</v>
+        <v>2.679573755869223</v>
       </c>
       <c r="D3" t="n">
-        <v>16.28649747490233</v>
+        <v>2.646555839671629</v>
       </c>
       <c r="E3" t="n">
-        <v>35.80354550179531</v>
+        <v>5.818076144041738</v>
       </c>
       <c r="F3" t="n">
-        <v>20.41757420637694</v>
+        <v>3.317855808536253</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>29.6601165439973</v>
+        <v>4.819768938399561</v>
       </c>
       <c r="D4" t="n">
-        <v>26.72545602978553</v>
+        <v>4.34288660484015</v>
       </c>
       <c r="E4" t="n">
-        <v>35.80354550179531</v>
+        <v>5.818076144041738</v>
       </c>
       <c r="F4" t="n">
-        <v>20.41757420637694</v>
+        <v>3.317855808536253</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>18.78047117446282</v>
+        <v>3.051826565850209</v>
       </c>
       <c r="D5" t="n">
-        <v>10.52163456856072</v>
+        <v>1.709765617391116</v>
       </c>
       <c r="E5" t="n">
-        <v>35.80354550179531</v>
+        <v>5.818076144041738</v>
       </c>
       <c r="F5" t="n">
-        <v>20.41757420637694</v>
+        <v>3.317855808536253</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>56.96340493288297</v>
+        <v>9.256553301593483</v>
       </c>
       <c r="D6" t="n">
-        <v>15.94924079472741</v>
+        <v>2.591751629143204</v>
       </c>
       <c r="E6" t="n">
-        <v>35.80354550179531</v>
+        <v>5.818076144041738</v>
       </c>
       <c r="F6" t="n">
-        <v>20.41757420637694</v>
+        <v>3.317855808536253</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>99.476906425282</v>
+        <v>16.16499729410832</v>
       </c>
       <c r="D7" t="n">
-        <v>55.07267925205745</v>
+        <v>8.949310378459337</v>
       </c>
       <c r="E7" t="n">
-        <v>35.80354550179531</v>
+        <v>5.818076144041738</v>
       </c>
       <c r="F7" t="n">
-        <v>20.41757420637694</v>
+        <v>3.317855808536253</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>110.9438426009155</v>
+        <v>18.02837442264877</v>
       </c>
       <c r="D8" t="n">
-        <v>62.77014689057709</v>
+        <v>10.20014886971878</v>
       </c>
       <c r="E8" t="n">
-        <v>35.80354550179531</v>
+        <v>5.818076144041738</v>
       </c>
       <c r="F8" t="n">
-        <v>20.41757420637694</v>
+        <v>3.317855808536253</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
